--- a/demo/registers/ServiceCentre_Repairs.xlsx
+++ b/demo/registers/ServiceCentre_Repairs.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="162">
   <si>
     <t>SKU</t>
   </si>
@@ -89,6 +89,15 @@
     <t>Returned On</t>
   </si>
   <si>
+    <t>Board Model</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Fault Category</t>
+  </si>
+  <si>
     <t>T-5000</t>
   </si>
   <si>
@@ -107,151 +116,196 @@
     <t>Rahul</t>
   </si>
   <si>
+    <t>PSU-48V</t>
+  </si>
+  <si>
+    <t>Metro Elevators</t>
+  </si>
+  <si>
+    <t>Trace/pad damage</t>
+  </si>
+  <si>
     <t>T-5001</t>
   </si>
   <si>
+    <t>Bhavna</t>
+  </si>
+  <si>
+    <t>PCB-30001</t>
+  </si>
+  <si>
+    <t>Overheating</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>MCB-200 controller</t>
+  </si>
+  <si>
+    <t>Bharat Textiles</t>
+  </si>
+  <si>
+    <t>Solder joint</t>
+  </si>
+  <si>
+    <t>T-5002</t>
+  </si>
+  <si>
+    <t>Farhan</t>
+  </si>
+  <si>
+    <t>PCB-30002</t>
+  </si>
+  <si>
+    <t>Display dead</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Component failure</t>
+  </si>
+  <si>
+    <t>T-5003</t>
+  </si>
+  <si>
+    <t>Esha</t>
+  </si>
+  <si>
+    <t>PCB-30003</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>T-5004</t>
+  </si>
+  <si>
+    <t>Chirag</t>
+  </si>
+  <si>
+    <t>PCB-30004</t>
+  </si>
+  <si>
+    <t>Firmware</t>
+  </si>
+  <si>
+    <t>T-5005</t>
+  </si>
+  <si>
+    <t>PCB-30005</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>VFD drive card</t>
+  </si>
+  <si>
+    <t>T-5006</t>
+  </si>
+  <si>
+    <t>Harsh</t>
+  </si>
+  <si>
+    <t>PCB-30006</t>
+  </si>
+  <si>
+    <t>Returned</t>
+  </si>
+  <si>
+    <t>Sunrise Plastics</t>
+  </si>
+  <si>
+    <t>T-5007</t>
+  </si>
+  <si>
+    <t>Gauri</t>
+  </si>
+  <si>
+    <t>PCB-30007</t>
+  </si>
+  <si>
+    <t>T-5008</t>
+  </si>
+  <si>
+    <t>PCB-30008</t>
+  </si>
+  <si>
+    <t>T-5009</t>
+  </si>
+  <si>
+    <t>PCB-30009</t>
+  </si>
+  <si>
+    <t>Sanctioned</t>
+  </si>
+  <si>
+    <t>T-5010</t>
+  </si>
+  <si>
+    <t>PCB-30010</t>
+  </si>
+  <si>
+    <t>Acme Pumps</t>
+  </si>
+  <si>
+    <t>T-5011</t>
+  </si>
+  <si>
+    <t>PCB-30011</t>
+  </si>
+  <si>
+    <t>Short circuit</t>
+  </si>
+  <si>
+    <t>T-5012</t>
+  </si>
+  <si>
     <t>Anil</t>
   </si>
   <si>
-    <t>PCB-30001</t>
+    <t>PCB-30012</t>
+  </si>
+  <si>
+    <t>T-5013</t>
+  </si>
+  <si>
+    <t>PCB-30013</t>
+  </si>
+  <si>
+    <t>HMI panel board</t>
+  </si>
+  <si>
+    <t>T-5014</t>
+  </si>
+  <si>
+    <t>PCB-30014</t>
+  </si>
+  <si>
+    <t>T-5015</t>
+  </si>
+  <si>
+    <t>PCB-30015</t>
+  </si>
+  <si>
+    <t>T-5016</t>
+  </si>
+  <si>
+    <t>PCB-30016</t>
+  </si>
+  <si>
+    <t>T-5017</t>
+  </si>
+  <si>
+    <t>PCB-30017</t>
   </si>
   <si>
     <t>Relay chatter</t>
-  </si>
-  <si>
-    <t>Closed</t>
-  </si>
-  <si>
-    <t>T-5002</t>
-  </si>
-  <si>
-    <t>PCB-30002</t>
-  </si>
-  <si>
-    <t>Display dead</t>
-  </si>
-  <si>
-    <t>Sanctioned</t>
-  </si>
-  <si>
-    <t>T-5003</t>
-  </si>
-  <si>
-    <t>Farhan</t>
-  </si>
-  <si>
-    <t>PCB-30003</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>T-5004</t>
-  </si>
-  <si>
-    <t>Gauri</t>
-  </si>
-  <si>
-    <t>PCB-30004</t>
-  </si>
-  <si>
-    <t>Overheating</t>
-  </si>
-  <si>
-    <t>T-5005</t>
-  </si>
-  <si>
-    <t>Chirag</t>
-  </si>
-  <si>
-    <t>PCB-30005</t>
-  </si>
-  <si>
-    <t>Returned</t>
-  </si>
-  <si>
-    <t>Priya</t>
-  </si>
-  <si>
-    <t>T-5006</t>
-  </si>
-  <si>
-    <t>PCB-30006</t>
-  </si>
-  <si>
-    <t>Rejected</t>
-  </si>
-  <si>
-    <t>T-5007</t>
-  </si>
-  <si>
-    <t>PCB-30007</t>
-  </si>
-  <si>
-    <t>T-5008</t>
-  </si>
-  <si>
-    <t>PCB-30008</t>
-  </si>
-  <si>
-    <t>T-5009</t>
-  </si>
-  <si>
-    <t>Harsh</t>
-  </si>
-  <si>
-    <t>PCB-30009</t>
-  </si>
-  <si>
-    <t>T-5010</t>
-  </si>
-  <si>
-    <t>PCB-30010</t>
-  </si>
-  <si>
-    <t>T-5011</t>
-  </si>
-  <si>
-    <t>PCB-30011</t>
-  </si>
-  <si>
-    <t>T-5012</t>
-  </si>
-  <si>
-    <t>Bhavna</t>
-  </si>
-  <si>
-    <t>PCB-30012</t>
-  </si>
-  <si>
-    <t>T-5013</t>
-  </si>
-  <si>
-    <t>PCB-30013</t>
-  </si>
-  <si>
-    <t>T-5014</t>
-  </si>
-  <si>
-    <t>PCB-30014</t>
-  </si>
-  <si>
-    <t>T-5015</t>
-  </si>
-  <si>
-    <t>PCB-30015</t>
-  </si>
-  <si>
-    <t>T-5016</t>
-  </si>
-  <si>
-    <t>PCB-30016</t>
-  </si>
-  <si>
-    <t>T-5017</t>
-  </si>
-  <si>
-    <t>PCB-30017</t>
   </si>
   <si>
     <t>T-5018</t>
@@ -945,7 +999,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -958,9 +1012,10 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12" style="1" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
@@ -994,13 +1049,22 @@
       <c r="K1" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -1009,16 +1073,16 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I2" s="1">
         <v>38</v>
@@ -1027,211 +1091,274 @@
         <f>D2*I2</f>
         <v>114</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I3" s="1">
-        <v>12</v>
+        <v>2400</v>
       </c>
       <c r="J3" s="1">
         <f>D3*I3</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7200</v>
+      </c>
+      <c r="L3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I4" s="1">
-        <v>2400</v>
+        <v>420</v>
       </c>
       <c r="J4" s="1">
         <f>D4*I4</f>
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1260</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
       </c>
       <c r="I5" s="1">
         <v>420</v>
       </c>
       <c r="J5" s="1">
         <f>D5*I5</f>
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1680</v>
+      </c>
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I6" s="1">
         <v>12</v>
       </c>
       <c r="J6" s="1">
         <f>D6*I6</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1">
-        <v>38</v>
+        <v>2400</v>
       </c>
       <c r="J7" s="1">
         <f>D7*I7</f>
-        <v>38</v>
-      </c>
-      <c r="K7" s="4">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2400</v>
+      </c>
+      <c r="L7" t="s">
+        <v>63</v>
+      </c>
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I8" s="1">
-        <v>12</v>
+        <v>2400</v>
       </c>
       <c r="J8" s="1">
         <f>D8*I8</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9600</v>
+      </c>
+      <c r="K8" s="4">
+        <v>46241</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
@@ -1240,16 +1367,16 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
         <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I9" s="1">
         <v>12</v>
@@ -1258,754 +1385,967 @@
         <f>D9*I9</f>
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" t="s">
+        <v>68</v>
+      </c>
+      <c r="N9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I10" s="1">
-        <v>38</v>
+        <v>420</v>
       </c>
       <c r="J10" s="1">
         <f>D10*I10</f>
+        <v>1260</v>
+      </c>
+      <c r="K10" s="4">
+        <v>46243</v>
+      </c>
+      <c r="L10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-      <c r="E11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" t="s">
-        <v>51</v>
-      </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I11" s="1">
-        <v>2400</v>
+        <v>150</v>
       </c>
       <c r="J11" s="1">
         <f>D11*I11</f>
-        <v>9600</v>
-      </c>
-      <c r="K11" s="4">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+      <c r="L11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11" t="s">
+        <v>68</v>
+      </c>
+      <c r="N11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I12" s="1">
-        <v>12</v>
+        <v>3100</v>
       </c>
       <c r="J12" s="1">
         <f>D12*I12</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>3100</v>
+      </c>
+      <c r="L12" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I13" s="1">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="J13" s="1">
         <f>D13*I13</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="L13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" t="s">
+        <v>79</v>
+      </c>
+      <c r="N13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H14" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I14" s="1">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="J14" s="1">
         <f>D14*I14</f>
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+      <c r="L14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" t="s">
+        <v>79</v>
+      </c>
+      <c r="N14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I15" s="1">
-        <v>3100</v>
+        <v>2400</v>
       </c>
       <c r="J15" s="1">
         <f>D15*I15</f>
-        <v>6200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4800</v>
+      </c>
+      <c r="L15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" t="s">
+        <v>79</v>
+      </c>
+      <c r="N15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I16" s="1">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="J16" s="1">
         <f>D16*I16</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="K16" s="4">
+        <v>46249</v>
+      </c>
+      <c r="L16" t="s">
+        <v>34</v>
+      </c>
+      <c r="M16" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I17" s="1">
         <v>3100</v>
       </c>
       <c r="J17" s="1">
         <f>D17*I17</f>
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6200</v>
+      </c>
+      <c r="L17" t="s">
+        <v>34</v>
+      </c>
+      <c r="M17" t="s">
+        <v>44</v>
+      </c>
+      <c r="N17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s">
         <v>49</v>
       </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" t="s">
-        <v>28</v>
-      </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="H18" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I18" s="1">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="J18" s="1">
         <f>D18*I18</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="K18" s="4">
+        <v>46251</v>
+      </c>
+      <c r="L18" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" t="s">
+        <v>79</v>
+      </c>
+      <c r="N18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I19" s="1">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="J19" s="1">
         <f>D19*I19</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+      <c r="K19" s="4">
+        <v>46252</v>
+      </c>
+      <c r="L19" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" t="s">
+        <v>35</v>
+      </c>
+      <c r="N19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I20" s="1">
         <v>150</v>
       </c>
       <c r="J20" s="1">
         <f>D20*I20</f>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="L20" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" t="s">
+        <v>68</v>
+      </c>
+      <c r="N20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I21" s="1">
-        <v>2400</v>
+        <v>150</v>
       </c>
       <c r="J21" s="1">
         <f>D21*I21</f>
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="L21" t="s">
+        <v>63</v>
+      </c>
+      <c r="M21" t="s">
+        <v>35</v>
+      </c>
+      <c r="N21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G22" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I22" s="1">
         <v>3100</v>
       </c>
       <c r="J22" s="1">
         <f>D22*I22</f>
-        <v>3100</v>
-      </c>
-      <c r="K22" s="4">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12400</v>
+      </c>
+      <c r="L22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M22" t="s">
+        <v>44</v>
+      </c>
+      <c r="N22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G23" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I23" s="1">
         <v>38</v>
       </c>
       <c r="J23" s="1">
         <f>D23*I23</f>
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="K23" s="4">
         <v>46256</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>43</v>
+      </c>
+      <c r="M23" t="s">
+        <v>44</v>
+      </c>
+      <c r="N23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D24">
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="G24" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="H24" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I24" s="1">
-        <v>3100</v>
+        <v>150</v>
       </c>
       <c r="J24" s="1">
         <f>D24*I24</f>
-        <v>9300</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+      <c r="K24" s="4">
+        <v>46257</v>
+      </c>
+      <c r="L24" t="s">
+        <v>43</v>
+      </c>
+      <c r="M24" t="s">
+        <v>44</v>
+      </c>
+      <c r="N24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I25" s="1">
-        <v>38</v>
+        <v>420</v>
       </c>
       <c r="J25" s="1">
         <f>D25*I25</f>
-        <v>76</v>
-      </c>
-      <c r="K25" s="4">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1260</v>
+      </c>
+      <c r="L25" t="s">
+        <v>34</v>
+      </c>
+      <c r="M25" t="s">
+        <v>44</v>
+      </c>
+      <c r="N25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="H26" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I26" s="1">
-        <v>12</v>
+        <v>2400</v>
       </c>
       <c r="J26" s="1">
         <f>D26*I26</f>
-        <v>36</v>
+        <v>2400</v>
       </c>
       <c r="K26" s="4">
         <v>46259</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" t="s">
+        <v>43</v>
+      </c>
+      <c r="M26" t="s">
+        <v>79</v>
+      </c>
+      <c r="N26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H27" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I27" s="1">
-        <v>3100</v>
+        <v>38</v>
       </c>
       <c r="J27" s="1">
         <f>D27*I27</f>
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="L27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M27" t="s">
+        <v>79</v>
+      </c>
+      <c r="N27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" t="s">
         <v>97</v>
       </c>
-      <c r="F28" t="s">
-        <v>34</v>
-      </c>
       <c r="G28" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I28" s="1">
         <v>38</v>
       </c>
       <c r="J28" s="1">
         <f>D28*I28</f>
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="L28" t="s">
+        <v>34</v>
+      </c>
+      <c r="M28" t="s">
+        <v>79</v>
+      </c>
+      <c r="N28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G29" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="H29" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I29" s="1">
-        <v>3100</v>
+        <v>420</v>
       </c>
       <c r="J29" s="1">
         <f>D29*I29</f>
-        <v>9300</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1680</v>
+      </c>
+      <c r="K29" s="4">
+        <v>46237</v>
+      </c>
+      <c r="L29" t="s">
+        <v>43</v>
+      </c>
+      <c r="M29" t="s">
+        <v>68</v>
+      </c>
+      <c r="N29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="F30" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H30" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I30" s="1">
-        <v>3100</v>
+        <v>420</v>
       </c>
       <c r="J30" s="1">
         <f>D30*I30</f>
-        <v>12400</v>
-      </c>
-      <c r="K30" s="4">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1680</v>
+      </c>
+      <c r="L30" t="s">
+        <v>34</v>
+      </c>
+      <c r="M30" t="s">
+        <v>68</v>
+      </c>
+      <c r="N30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="F31" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G31" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H31" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I31" s="1">
-        <v>12</v>
+        <v>420</v>
       </c>
       <c r="J31" s="1">
         <f>D31*I31</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+      <c r="L31" t="s">
+        <v>88</v>
+      </c>
+      <c r="M31" t="s">
+        <v>44</v>
+      </c>
+      <c r="N31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
@@ -2014,16 +2354,16 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F32" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H32" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I32" s="1">
         <v>3100</v>
@@ -2032,638 +2372,815 @@
         <f>D32*I32</f>
         <v>3100</v>
       </c>
-      <c r="K32" s="4">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L32" t="s">
+        <v>43</v>
+      </c>
+      <c r="M32" t="s">
+        <v>68</v>
+      </c>
+      <c r="N32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="G33" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H33" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I33" s="1">
-        <v>420</v>
+        <v>12</v>
       </c>
       <c r="J33" s="1">
         <f>D33*I33</f>
-        <v>840</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="L33" t="s">
+        <v>34</v>
+      </c>
+      <c r="M33" t="s">
+        <v>68</v>
+      </c>
+      <c r="N33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="G34" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="H34" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I34" s="1">
-        <v>150</v>
+        <v>3100</v>
       </c>
       <c r="J34" s="1">
         <f>D34*I34</f>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9300</v>
+      </c>
+      <c r="K34" s="4">
+        <v>46242</v>
+      </c>
+      <c r="L34" t="s">
+        <v>63</v>
+      </c>
+      <c r="M34" t="s">
+        <v>44</v>
+      </c>
+      <c r="N34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="F35" t="s">
+        <v>40</v>
+      </c>
+      <c r="G35" t="s">
+        <v>67</v>
+      </c>
+      <c r="H35" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="1">
         <v>38</v>
-      </c>
-      <c r="G35" t="s">
-        <v>35</v>
-      </c>
-      <c r="H35" t="s">
-        <v>30</v>
-      </c>
-      <c r="I35" s="1">
-        <v>150</v>
       </c>
       <c r="J35" s="1">
         <f>D35*I35</f>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="K35" s="4">
+        <v>46243</v>
+      </c>
+      <c r="L35" t="s">
+        <v>63</v>
+      </c>
+      <c r="M35" t="s">
+        <v>79</v>
+      </c>
+      <c r="N35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36" t="s">
+        <v>131</v>
+      </c>
+      <c r="F36" t="s">
         <v>49</v>
       </c>
-      <c r="C36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" t="s">
-        <v>47</v>
-      </c>
       <c r="G36" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I36" s="1">
-        <v>150</v>
+        <v>3100</v>
       </c>
       <c r="J36" s="1">
         <f>D36*I36</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12400</v>
+      </c>
+      <c r="L36" t="s">
+        <v>88</v>
+      </c>
+      <c r="M36" t="s">
+        <v>44</v>
+      </c>
+      <c r="N36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="G37" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H37" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I37" s="1">
         <v>3100</v>
       </c>
       <c r="J37" s="1">
         <f>D37*I37</f>
-        <v>6200</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9300</v>
+      </c>
+      <c r="K37" s="4">
+        <v>46245</v>
+      </c>
+      <c r="L37" t="s">
+        <v>43</v>
+      </c>
+      <c r="M37" t="s">
+        <v>35</v>
+      </c>
+      <c r="N37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="F38" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="G38" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H38" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I38" s="1">
-        <v>2400</v>
+        <v>150</v>
       </c>
       <c r="J38" s="1">
         <f>D38*I38</f>
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="L38" t="s">
+        <v>63</v>
+      </c>
+      <c r="M38" t="s">
+        <v>35</v>
+      </c>
+      <c r="N38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F39" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G39" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H39" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I39" s="1">
-        <v>2400</v>
+        <v>3100</v>
       </c>
       <c r="J39" s="1">
         <f>D39*I39</f>
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <v>3100</v>
+      </c>
+      <c r="K39" s="4">
+        <v>46247</v>
+      </c>
+      <c r="L39" t="s">
+        <v>34</v>
+      </c>
+      <c r="M39" t="s">
+        <v>68</v>
+      </c>
+      <c r="N39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F40" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H40" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I40" s="1">
-        <v>12</v>
+        <v>420</v>
       </c>
       <c r="J40" s="1">
         <f>D40*I40</f>
-        <v>24</v>
-      </c>
-      <c r="K40" s="4">
-        <v>46248</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+      <c r="L40" t="s">
+        <v>34</v>
+      </c>
+      <c r="M40" t="s">
+        <v>44</v>
+      </c>
+      <c r="N40" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="F41" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G41" t="s">
-        <v>39</v>
-      </c>
-      <c r="H41" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I41" s="1">
-        <v>420</v>
+        <v>3100</v>
       </c>
       <c r="J41" s="1">
         <f>D41*I41</f>
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9300</v>
+      </c>
+      <c r="L41" t="s">
+        <v>34</v>
+      </c>
+      <c r="M41" t="s">
+        <v>35</v>
+      </c>
+      <c r="N41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="F42" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G42" t="s">
-        <v>55</v>
-      </c>
-      <c r="H42" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I42" s="1">
-        <v>12</v>
+        <v>3100</v>
       </c>
       <c r="J42" s="1">
         <f>D42*I42</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6200</v>
+      </c>
+      <c r="L42" t="s">
+        <v>43</v>
+      </c>
+      <c r="M42" t="s">
+        <v>44</v>
+      </c>
+      <c r="N42" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="F43" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G43" t="s">
-        <v>39</v>
-      </c>
-      <c r="H43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I43" s="1">
-        <v>38</v>
+        <v>420</v>
       </c>
       <c r="J43" s="1">
         <f>D43*I43</f>
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+      <c r="L43" t="s">
+        <v>88</v>
+      </c>
+      <c r="M43" t="s">
+        <v>44</v>
+      </c>
+      <c r="N43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="F44" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G44" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H44" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I44" s="1">
-        <v>420</v>
+        <v>2400</v>
       </c>
       <c r="J44" s="1">
         <f>D44*I44</f>
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2400</v>
+      </c>
+      <c r="L44" t="s">
+        <v>63</v>
+      </c>
+      <c r="M44" t="s">
+        <v>44</v>
+      </c>
+      <c r="N44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
         <v>7</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="F45" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G45" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H45" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I45" s="1">
         <v>3100</v>
       </c>
       <c r="J45" s="1">
         <f>D45*I45</f>
-        <v>12400</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6200</v>
+      </c>
+      <c r="L45" t="s">
+        <v>63</v>
+      </c>
+      <c r="M45" t="s">
+        <v>79</v>
+      </c>
+      <c r="N45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="F46" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="G46" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H46" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I46" s="1">
         <v>420</v>
       </c>
       <c r="J46" s="1">
         <f>D46*I46</f>
-        <v>1680</v>
-      </c>
-      <c r="K46" s="4">
-        <v>46254</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1260</v>
+      </c>
+      <c r="L46" t="s">
+        <v>43</v>
+      </c>
+      <c r="M46" t="s">
+        <v>35</v>
+      </c>
+      <c r="N46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C47" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G47" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H47" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I47" s="1">
-        <v>3100</v>
+        <v>2400</v>
       </c>
       <c r="J47" s="1">
         <f>D47*I47</f>
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4800</v>
+      </c>
+      <c r="L47" t="s">
+        <v>88</v>
+      </c>
+      <c r="M47" t="s">
+        <v>68</v>
+      </c>
+      <c r="N47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="F48" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="G48" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H48" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I48" s="1">
-        <v>3100</v>
+        <v>420</v>
       </c>
       <c r="J48" s="1">
         <f>D48*I48</f>
-        <v>12400</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+        <v>840</v>
+      </c>
+      <c r="K48" s="4">
+        <v>46256</v>
+      </c>
+      <c r="L48" t="s">
+        <v>43</v>
+      </c>
+      <c r="M48" t="s">
+        <v>35</v>
+      </c>
+      <c r="N48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C49" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="F49" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="G49" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="H49" t="s">
+        <v>33</v>
       </c>
       <c r="I49" s="1">
-        <v>3100</v>
+        <v>420</v>
       </c>
       <c r="J49" s="1">
         <f>D49*I49</f>
-        <v>9300</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <v>840</v>
+      </c>
+      <c r="L49" t="s">
+        <v>63</v>
+      </c>
+      <c r="M49" t="s">
+        <v>35</v>
+      </c>
+      <c r="N49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="B50" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C50" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="F50" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H50" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I50" s="1">
-        <v>12</v>
+        <v>420</v>
       </c>
       <c r="J50" s="1">
         <f>D50*I50</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+        <v>840</v>
+      </c>
+      <c r="L50" t="s">
+        <v>43</v>
+      </c>
+      <c r="M50" t="s">
+        <v>68</v>
+      </c>
+      <c r="N50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="F51" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="G51" t="s">
-        <v>29</v>
-      </c>
-      <c r="H51" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I51" s="1">
-        <v>3100</v>
+        <v>38</v>
       </c>
       <c r="J51" s="1">
         <f>D51*I51</f>
-        <v>9300</v>
+        <v>38</v>
+      </c>
+      <c r="L51" t="s">
+        <v>43</v>
+      </c>
+      <c r="M51" t="s">
+        <v>35</v>
+      </c>
+      <c r="N51" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
